--- a/services_forms/002_service_desk_satisfaction_survey--services_forms.xlsx
+++ b/services_forms/002_service_desk_satisfaction_survey--services_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1007,8 +1007,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_1_hour'}</t>
+          <t>less_than_1_hour</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less than 1 hour'}</t>
+          <t>Less than 1 hour</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'1-2_hours'}</t>
+          <t>1-2_hours</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '1-2 hours'}</t>
+          <t>1-2 hours</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'2-4_hours'}</t>
+          <t>2-4_hours</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '2-4 hours'}</t>
+          <t>2-4 hours</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'4-8_hours'}</t>
+          <t>4-8_hours</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '4-8 hours'}</t>
+          <t>4-8 hours</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1104,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'more_than_4_hours'}</t>
+          <t>more_than_4_hours</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'More than 4 hours'}</t>
+          <t>More than 4 hours</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_clear'}</t>
+          <t>very_clear</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very clear'}</t>
+          <t>Very clear</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'clear'}</t>
+          <t>clear</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Clear'}</t>
+          <t>Clear</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat_clear'}</t>
+          <t>somewhat_clear</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat clear'}</t>
+          <t>Somewhat clear</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_very_clear'}</t>
+          <t>not_very_clear</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not very clear'}</t>
+          <t>Not very clear</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'not_at_all_clear'}</t>
+          <t>not_at_all_clear</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Not at all clear'}</t>
+          <t>Not at all clear</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_helpful'}</t>
+          <t>very_helpful</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very helpful'}</t>
+          <t>Very helpful</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'helpful'}</t>
+          <t>helpful</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Helpful'}</t>
+          <t>Helpful</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'somewhat_helpful'}</t>
+          <t>somewhat_helpful</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Somewhat helpful'}</t>
+          <t>Somewhat helpful</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'not_very_helpful'}</t>
+          <t>not_very_helpful</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Not very helpful'}</t>
+          <t>Not very helpful</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'not_at_all_helpful'}</t>
+          <t>not_at_all_helpful</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Not at all helpful'}</t>
+          <t>Not at all helpful</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Dissatisfied'}</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'support_team'}</t>
+          <t>support_team</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Support team'}</t>
+          <t>Support team</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'team_members'}</t>
+          <t>team_members</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Team members'}</t>
+          <t>Team members</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'was_a_manager_involved_in_the_case?'}</t>
+          <t>was_a_manager_involved_in_the_case?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Was a manager involved in the case?'}</t>
+          <t>Was a manager involved in the case?</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
